--- a/artfynd/A 39526-2021 artfynd.xlsx
+++ b/artfynd/A 39526-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39526-2021 artfynd.xlsx
+++ b/artfynd/A 39526-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2399,1599 +2399,6 @@
           <t>Ecogain</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>113168514</v>
-      </c>
-      <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>562020</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6896825</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>113170304</v>
-      </c>
-      <c r="B17" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>561983</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6896800</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>113170570</v>
-      </c>
-      <c r="B18" t="n">
-        <v>79431</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>389</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Läderlappslav</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Collema nigrescens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>562149</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6896721</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>113168512</v>
-      </c>
-      <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>562092</v>
-      </c>
-      <c r="R19" t="n">
-        <v>6896858</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>113168510</v>
-      </c>
-      <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>562048</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6896768</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>113168776</v>
-      </c>
-      <c r="B21" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>562115</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6896828</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>113170500</v>
-      </c>
-      <c r="B22" t="n">
-        <v>97684</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>219874</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Nattviol</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>562128</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6896745</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>113170081</v>
-      </c>
-      <c r="B23" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>562125</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6896830</v>
-      </c>
-      <c r="S23" t="n">
-        <v>10</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>113168511</v>
-      </c>
-      <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>562125</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6896832</v>
-      </c>
-      <c r="S24" t="n">
-        <v>10</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>113168774</v>
-      </c>
-      <c r="B25" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>562129</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6896732</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>113168509</v>
-      </c>
-      <c r="B26" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>562112</v>
-      </c>
-      <c r="R26" t="n">
-        <v>6896759</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>113170302</v>
-      </c>
-      <c r="B27" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>562098</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6896851</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>113168508</v>
-      </c>
-      <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>562189</v>
-      </c>
-      <c r="R28" t="n">
-        <v>6896736</v>
-      </c>
-      <c r="S28" t="n">
-        <v>10</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>113168513</v>
-      </c>
-      <c r="B29" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>562043</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6896877</v>
-      </c>
-      <c r="S29" t="n">
-        <v>10</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39526-2021 artfynd.xlsx
+++ b/artfynd/A 39526-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105545650</v>
+        <v>105545619</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>389</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huds.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562128.9037118653</v>
+        <v>562149</v>
       </c>
       <c r="R2" t="n">
-        <v>6896731.518800999</v>
+        <v>6896721</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105545533</v>
+        <v>105545650</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,43 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562043.9413097494</v>
+        <v>562129</v>
       </c>
       <c r="R3" t="n">
-        <v>6896876.552104953</v>
+        <v>6896732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +844,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105545619</v>
+        <v>105545652</v>
       </c>
       <c r="B4" t="n">
-        <v>78477</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>389</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>562148.7329140297</v>
+        <v>562115</v>
       </c>
       <c r="R4" t="n">
-        <v>6896721.146052551</v>
+        <v>6896828</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,19 +945,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,59 +978,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105545531</v>
+        <v>105545642</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>562124.7168149732</v>
+        <v>562075</v>
       </c>
       <c r="R5" t="n">
-        <v>6896831.82035285</v>
+        <v>6896898</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1046,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,42 +1079,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105545534</v>
+        <v>105545516</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>562019.6384581947</v>
+        <v>562128</v>
       </c>
       <c r="R6" t="n">
-        <v>6896825.216164473</v>
+        <v>6896745</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1239,19 +1156,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,42 +1189,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105545516</v>
+        <v>105545528</v>
       </c>
       <c r="B7" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1331,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562127.7279732409</v>
+        <v>562189</v>
       </c>
       <c r="R7" t="n">
-        <v>6896744.569874503</v>
+        <v>6896736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1364,19 +1266,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,50 +1299,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105545652</v>
+        <v>105545529</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562115.4463063527</v>
+        <v>562112</v>
       </c>
       <c r="R8" t="n">
-        <v>6896827.44762328</v>
+        <v>6896759</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,19 +1372,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,15 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105545528</v>
+        <v>105545530</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1435,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1572,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>562188.6805707676</v>
+        <v>562048</v>
       </c>
       <c r="R9" t="n">
-        <v>6896735.422658073</v>
+        <v>6896768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,19 +1482,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,42 +1515,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105545465</v>
+        <v>105545531</v>
       </c>
       <c r="B10" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1697,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>562124.742626484</v>
+        <v>562125</v>
       </c>
       <c r="R10" t="n">
-        <v>6896830.420215636</v>
+        <v>6896832</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,19 +1592,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,15 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105545529</v>
+        <v>105545532</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,7 +1653,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1818,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>562112.5128321514</v>
+        <v>562092</v>
       </c>
       <c r="R11" t="n">
-        <v>6896758.295872482</v>
+        <v>6896858</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1851,19 +1702,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105545530</v>
+        <v>105545533</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1765,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1943,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562048.2804544861</v>
+        <v>562043</v>
       </c>
       <c r="R12" t="n">
-        <v>6896767.8508684</v>
+        <v>6896877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1976,19 +1812,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2019,62 +1845,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105545480</v>
+        <v>105545534</v>
       </c>
       <c r="B13" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>562098.1727975875</v>
+        <v>562020</v>
       </c>
       <c r="R13" t="n">
-        <v>6896851.406505012</v>
+        <v>6896825</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2104,28 +1922,17 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2148,59 +1955,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105545532</v>
+        <v>105545480</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562091.0329020704</v>
+        <v>562098</v>
       </c>
       <c r="R14" t="n">
-        <v>6896858.277957276</v>
+        <v>6896851</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2230,27 +2035,18 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2276,12 +2072,7 @@
         <v>105545481</v>
       </c>
       <c r="B15" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2325,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561983.1690220768</v>
+        <v>561983</v>
       </c>
       <c r="R15" t="n">
-        <v>6896799.800928142</v>
+        <v>6896800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2358,19 +2149,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,6 +2176,116 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105545465</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>562125</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6896830</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
